--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,53 +1,457 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="17860" windowHeight="10480"/>
   </bookViews>
   <sheets>
-    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Новые товары Ozon" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$N$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>НОВЫЙ артикул (offer_id) — придумайте сами, уникальный</t>
+  </si>
+  <si>
+    <t>Образец: артикул похожего товара, уже продающегося на Ozon</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Цена, ₽</t>
+  </si>
+  <si>
+    <t>Цена до скидки, ₽ (необязательно)</t>
+  </si>
+  <si>
+    <t>Штрихкод (необязательно — можно оставить пустым)</t>
+  </si>
+  <si>
+    <t>Вес, г (пусто = как у образца)</t>
+  </si>
+  <si>
+    <t>Длина, мм (пусто = как у образца)</t>
+  </si>
+  <si>
+    <t>Ширина, мм (пусто = как у образца)</t>
+  </si>
+  <si>
+    <t>Высота, мм (пусто = как у образца)</t>
+  </si>
+  <si>
+    <t>Фото: ссылки через | (заполняется автоматически attach-ozon-new-photos)</t>
+  </si>
+  <si>
+    <t>Видео: ссылка на .mp4/.mov, необязательно, ЭКСПЕРИМЕНТАЛЬНО</t>
+  </si>
+  <si>
+    <t>Заметки</t>
+  </si>
+  <si>
+    <t>TEST001</t>
+  </si>
+  <si>
+    <t>02E305045</t>
+  </si>
+  <si>
+    <t>Тестовый товар — не публикуется</t>
+  </si>
+  <si>
+    <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -55,86 +459,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -417,109 +1048,93 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>НОВЫЙ артикул (offer_id) — придумайте сами, уникальный</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Образец: артикул похожего товара, уже продающегося на Ozon</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Цена, ₽</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Цена до скидки, ₽ (необязательно)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Штрихкод (необязательно — можно оставить пустым)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Вес, г (пусто = как у образца)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Длина, мм (пусто = как у образца)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ширина, мм (пусто = как у образца)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Высота, мм (пусто = как у образца)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Фото: ссылки через | (заполняется автоматически attach-ozon-new-photos)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Видео: ссылка на .mp4/.mov, необязательно, ЭКСПЕРИМЕНТАЛЬНО</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Заметки</t>
-        </is>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:N1">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Новые товары Ozon" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -65,7 +65,7 @@
     <t>TEST001</t>
   </si>
   <si>
-    <t>02E305045</t>
+    <t>02e305045</t>
   </si>
   <si>
     <t>Тестовый товар — не публикуется</t>
@@ -79,12 +79,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,45 +109,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,8 +130,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -176,9 +154,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,58 +163,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,6 +183,66 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -266,37 +259,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -308,19 +391,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,115 +427,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +457,48 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,33 +522,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,163 +550,148 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1131,7 +1124,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1">
+  <autoFilter ref="A1:N2">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,262 +1,194 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="17860" windowHeight="10480"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17860" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Новые товары Ozon" sheetId="1" r:id="rId1"/>
+    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$O$1</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>НОВЫЙ артикул (offer_id) — придумайте сами, уникальный</t>
-  </si>
-  <si>
-    <t>Образец: артикул похожего товара, уже продающегося на Ozon</t>
-  </si>
-  <si>
-    <t>Название</t>
-  </si>
-  <si>
-    <t>Описание</t>
-  </si>
-  <si>
-    <t>Цена, ₽</t>
-  </si>
-  <si>
-    <t>Цена до скидки, ₽ (необязательно)</t>
-  </si>
-  <si>
-    <t>Штрихкод (необязательно — можно оставить пустым)</t>
-  </si>
-  <si>
-    <t>Код ТН ВЭД — ОБЯЗАТЕЛЬНО для реальной продажи (посмотрите такой же код у образца в кабинете Ozon)</t>
-  </si>
-  <si>
-    <t>Вес, г (пусто = как у образца)</t>
-  </si>
-  <si>
-    <t>Длина, мм (пусто = как у образца)</t>
-  </si>
-  <si>
-    <t>Ширина, мм (пусто = как у образца)</t>
-  </si>
-  <si>
-    <t>Высота, мм (пусто = как у образца)</t>
-  </si>
-  <si>
-    <t>Фото: ссылки через | (заполняется автоматически attach-ozon-new-photos)</t>
-  </si>
-  <si>
-    <t>Видео: ссылка на .mp4/.mov, необязательно, ЭКСПЕРИМЕНТАЛЬНО</t>
-  </si>
-  <si>
-    <t>Заметки</t>
-  </si>
-  <si>
-    <t>TEST001</t>
-  </si>
-  <si>
-    <t>02e305045</t>
-  </si>
-  <si>
-    <t>Тестовый товар — не публикуется</t>
-  </si>
-  <si>
-    <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -562,155 +494,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,11 +696,74 @@
     <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1055,95 +1050,138 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="55" customWidth="1"/>
-    <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="15" max="15" width="25" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="8"/>
+    <col width="14" customWidth="1" min="9" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НОВЫЙ артикул (offer_id) — придумайте сами, уникальный</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Образец: артикул похожего товара, уже продающегося на Ozon</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цена, ₽</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Цена до скидки, ₽ (необязательно)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Штрихкод (необязательно — можно оставить пустым)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Код ТН ВЭД — ОБЯЗАТЕЛЬНО для реальной продажи (посмотрите такой же код у образца в кабинете Ozon)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Вес, г (пусто = как у образца)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Длина, мм (пусто = как у образца)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, мм (пусто = как у образца)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Высота, мм (пусто = как у образца)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Фото: ссылки через | (заполняется автоматически attach-ozon-new-photos)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Видео: ссылка на .mp4/.mov, необязательно, ЭКСПЕРИМЕНТАЛЬНО</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Заметки</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>02e305045</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Тестовый товар — не публикуется</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>100</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>8421230000</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TEST001_1.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1176,7 +1176,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TEST001_1.jpg</t>
+          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TEST001_2.jpg</t>
         </is>
       </c>
     </row>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1176,7 +1176,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/antongrigorenko844-prog/marketplace-agent/main/photos/TEST001_2.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
         </is>
       </c>
     </row>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,512 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0am325091e-set</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0am325091e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Комплект: 2 штока 0AM325091E (101мм) усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0am325091f-set</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0am325091f</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Комплект: 2 штока 0AM325091F (99мм) короткие усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника + фильтр DSG7 DQ200 0AM/0CW, комплект</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника + фильтр + 2 пыльника штоков DSG7 DQ200 0AM/0CW, комплект</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника + фильтр + 2 пыльника + 2 сальника DSG7 DQ200 0AM/0CW, полный комплект</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 пыльника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 сальника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0am325025G</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект штоков VAG (2 пыльника + 2 сальника + 2 крышки) DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0am325025G</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Оригинальный комплект пыльников штоков VAG, 2 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Оригинальный комплект сальников штоков VAG, 2 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>123014-AF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0am325025j</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Оригинальные пластины на соленоиды Volkswagen мехатроника DQ200 DSG7 (без сепараторной пластины)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Усиленный алюминиевый сальник толкателя с гальваническим покрытием DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0am325025P</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Планки соленоидов DSG7 DQ200, комплект 2 шт на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0AM325587E</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0ambset</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Подшипники вилки 6-й передачи и заднего хода DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0am325066AC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Комплект толкателей вилок (поршней) 4 шт + сальники 4 шт DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1162,6 +1162,60 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A (одиночный сальник) вместе с фото ещё 3 других комплектов; вынесено в отдельную позицию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$O$1</definedName>
@@ -537,7 +537,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Мехатроник DQ250 DSG6 с платой 02E927770AL</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -559,7 +564,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Сальник привода (левый) DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -581,7 +591,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Сальник привода (правый) DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -606,6 +621,11 @@
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
@@ -628,6 +648,11 @@
           <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
@@ -647,7 +672,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30 6T40 6T45 6T50 Chevrolet Cruze, Opel</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -669,7 +699,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Комплект: 2 штока 0AM325091E (101мм) усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -691,7 +726,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Комплект: 2 штока 0AM325091F (99мм) короткие усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -713,7 +753,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр DSG7 DQ200 0AM/0CW, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -735,7 +780,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр + 2 пыльника штоков DSG7 DQ200 0AM/0CW, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -757,7 +807,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Усиленная плита мехатроника + фильтр + 2 пыльника + 2 сальника DSG7 DQ200 0AM/0CW, полный комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -779,7 +834,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 пыльника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -801,7 +861,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 сальника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -823,7 +888,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект штоков VAG (2 пыльника + 2 сальника + 2 крышки) DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -845,7 +915,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Оригинальный комплект пыльников штоков VAG, 2 шт DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -867,7 +942,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Оригинальный комплект сальников штоков VAG, 2 шт DSG7 DQ200</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -889,7 +969,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -914,6 +999,11 @@
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
@@ -933,7 +1023,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды Volkswagen мехатроника DQ200 DSG7 (без сепараторной пластины)</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -955,7 +1050,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый сальник толкателя с гальваническим покрытием DSG7 DQ200</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -980,6 +1080,11 @@
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
@@ -1002,6 +1107,11 @@
           <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
@@ -1021,7 +1131,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1043,7 +1158,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Планки соленоидов DSG7 DQ200, комплект 2 шт на весь мехатроник</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1068,6 +1188,11 @@
           <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
@@ -1087,7 +1212,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Подшипники вилки 6-й передачи и заднего хода DSG7 DQ200, комплект</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1109,7 +1239,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1131,7 +1266,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Комплект толкателей вилок (поршней) 4 шт + сальники 4 шт DSG7 DQ200, на весь мехатроник</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -1153,7 +1293,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -1185,7 +1330,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A (одиночный сальник) вместе с фото ещё 3 других комплектов; вынесено в отдельную позицию.</t>
+          <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
         </is>
       </c>
     </row>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -545,6 +545,11 @@
           <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
@@ -572,6 +577,11 @@
           <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
@@ -599,6 +609,11 @@
           <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
@@ -626,6 +641,11 @@
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
@@ -653,6 +673,11 @@
           <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
@@ -680,6 +705,11 @@
           <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
@@ -707,6 +737,11 @@
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
@@ -734,6 +769,11 @@
           <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
@@ -761,6 +801,11 @@
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
@@ -788,6 +833,11 @@
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -815,6 +865,11 @@
           <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -842,6 +897,11 @@
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -869,6 +929,11 @@
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.png</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -896,6 +961,11 @@
           <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
@@ -923,6 +993,11 @@
           <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
@@ -950,6 +1025,11 @@
           <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
@@ -977,6 +1057,11 @@
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
@@ -1004,6 +1089,11 @@
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
@@ -1031,6 +1121,11 @@
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
@@ -1058,6 +1153,11 @@
           <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
@@ -1085,6 +1185,11 @@
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
@@ -1112,6 +1217,11 @@
           <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
@@ -1139,6 +1249,11 @@
           <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
@@ -1166,6 +1281,11 @@
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
@@ -1193,6 +1313,11 @@
           <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
@@ -1220,6 +1345,11 @@
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
@@ -1247,6 +1377,11 @@
           <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
@@ -1274,6 +1409,11 @@
           <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
@@ -1301,6 +1441,11 @@
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
@@ -1328,6 +1473,11 @@
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
@@ -1353,6 +1503,11 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -540,6 +540,12 @@
           <t>Мехатроник DQ250 DSG6 с платой 02E927770AL</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>145000</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
@@ -562,6 +568,12 @@
           <t>Сальник привода (левый) DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1700</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
@@ -584,6 +596,12 @@
           <t>Сальник привода (правый) DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1700</v>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
@@ -606,6 +624,12 @@
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1700</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
@@ -628,6 +652,12 @@
           <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1700</v>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
@@ -650,6 +680,12 @@
           <t>Соленоиды АКПП 6T30 6T40 6T45 6T50 Chevrolet Cruze, Opel</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>3990</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6000</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
@@ -672,6 +708,12 @@
           <t>Комплект: 2 штока 0AM325091E (101мм) усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>10490</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15000</v>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
@@ -694,6 +736,12 @@
           <t>Комплект: 2 штока 0AM325091F (99мм) короткие усиленные + 2 втулки (гильзы) мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>10490</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15000</v>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
@@ -716,6 +764,12 @@
           <t>Усиленная плита мехатроника + фильтр DSG7 DQ200 0AM/0CW, комплект</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>9990</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14000</v>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
@@ -738,6 +792,12 @@
           <t>Усиленная плита мехатроника + фильтр + 2 пыльника штоков DSG7 DQ200 0AM/0CW, комплект</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>11990</v>
+      </c>
+      <c r="F11" t="n">
+        <v>17000</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -760,6 +820,12 @@
           <t>Усиленная плита мехатроника + фильтр + 2 пыльника + 2 сальника DSG7 DQ200 0AM/0CW, полный комплект</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19500</v>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -782,6 +848,12 @@
           <t>Усиленная плита + фильтр + 2 пыльника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>12990</v>
+      </c>
+      <c r="F13" t="n">
+        <v>18000</v>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -804,6 +876,12 @@
           <t>Усиленная плита + фильтр + 2 сальника ОРИГИНАЛ Volkswagen DSG7 DQ200, комплект</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>12990</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18000</v>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -826,6 +904,12 @@
           <t>Оригинальный ремкомплект штоков VAG (2 пыльника + 2 сальника + 2 крышки) DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>5490</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7500</v>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
@@ -848,6 +932,12 @@
           <t>Оригинальный комплект пыльников штоков VAG, 2 шт DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>2790</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4000</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
@@ -870,6 +960,12 @@
           <t>Оригинальный комплект сальников штоков VAG, 2 шт DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>2790</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4000</v>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
@@ -892,6 +988,12 @@
           <t>Оригинальный сальник штока VAG, 1 шт DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2500</v>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
@@ -906,13 +1008,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>123014-AF</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3000</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -936,6 +1044,12 @@
           <t>Оригинальные пластины на соленоиды Volkswagen мехатроника DQ200 DSG7 (без сепараторной пластины)</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4000</v>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
@@ -958,6 +1072,12 @@
           <t>Усиленный алюминиевый сальник толкателя с гальваническим покрытием DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>2990</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4500</v>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
@@ -980,6 +1100,12 @@
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7000</v>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
@@ -1002,6 +1128,12 @@
           <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>1690</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2800</v>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
@@ -1024,6 +1156,12 @@
           <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт (на 2 штока)</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2200</v>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
@@ -1046,6 +1184,12 @@
           <t>Планки соленоидов DSG7 DQ200, комплект 2 шт на весь мехатроник</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>3990</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5500</v>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
@@ -1068,6 +1212,12 @@
           <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>8890</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12000</v>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
@@ -1090,6 +1240,12 @@
           <t>Подшипники вилки 6-й передачи и заднего хода DSG7 DQ200, комплект</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>890</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1500</v>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
@@ -1112,6 +1268,12 @@
           <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>890</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1500</v>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
@@ -1134,6 +1296,12 @@
           <t>Комплект толкателей вилок (поршней) 4 шт + сальники 4 шт DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>9490</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13500</v>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
@@ -1148,13 +1316,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3879</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6000</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -1183,6 +1357,12 @@
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>3490</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5000</v>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A (одиночный сальник) вместе с фото ещё 3 других комплектов; вынесено в отдельную позицию.</t>
@@ -1209,6 +1389,12 @@
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
+      </c>
+      <c r="E32" t="n">
+        <v>11990</v>
+      </c>
+      <c r="F32" t="n">
+        <v>17000</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10490</v>
+        <v>8850</v>
       </c>
       <c r="F8" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10490</v>
+        <v>8850</v>
       </c>
       <c r="F9" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9990</v>
+        <v>7500</v>
       </c>
       <c r="F10" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11990</v>
+        <v>8500</v>
       </c>
       <c r="F11" t="n">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13990</v>
+        <v>9500</v>
       </c>
       <c r="F12" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12990</v>
+        <v>8500</v>
       </c>
       <c r="F13" t="n">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12990</v>
+        <v>8500</v>
       </c>
       <c r="F14" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5490</v>
+        <v>2850</v>
       </c>
       <c r="F15" t="n">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2790</v>
+        <v>1850</v>
       </c>
       <c r="F16" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2790</v>
+        <v>1890</v>
       </c>
       <c r="F17" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1990</v>
+        <v>1490</v>
       </c>
       <c r="F19" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2490</v>
+        <v>990</v>
       </c>
       <c r="F20" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2990</v>
+        <v>2490</v>
       </c>
       <c r="F21" t="n">
         <v>4500</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1490</v>
+        <v>950</v>
       </c>
       <c r="F24" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3990</v>
+        <v>2890</v>
       </c>
       <c r="F25" t="n">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="F27" t="n">
         <v>1500</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>890</v>
+        <v>1950</v>
       </c>
       <c r="F28" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9490</v>
+        <v>7400</v>
       </c>
       <c r="F29" t="n">
-        <v>13500</v>
+        <v>10000</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3490</v>
+        <v>1950</v>
       </c>
       <c r="F31" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>11990</v>
+        <v>8900</v>
       </c>
       <c r="F32" t="n">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1702,6 +1702,67 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0am325025G</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3990</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Цена — грубая оценка Клода (аналогичного готового комплекта именно с усиленными поршнями в файле раньше не было, ориентировался на цену поршня по отдельности + похожий комплект с сальниками вместо поршней) — проверьте и поправьте сами.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$O$1</definedName>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1729,6 +1729,11 @@
       <c r="F33" t="n">
         <v>13500</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1756,6 +1761,11 @@
       </c>
       <c r="F34" t="n">
         <v>6500</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -444,7 +448,9 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,1261 +526,1701 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Кол-во к продаже (остаток при создании — реально уходит в Ozon отдельной командой push-stock после push-ozon-new-cards)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Заметки</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Хэштеги / ключевые слова (через запятую, необязательно)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>02E927770AL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>118000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>145000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>salnikprivod-l</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>999</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
         </is>
       </c>
+      <c r="Q3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>salnikprivod-r</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>999</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
         </is>
       </c>
+      <c r="Q4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>salnikvhod</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>999</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
         </is>
       </c>
+      <c r="Q5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>salnikvihod</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
         </is>
       </c>
+      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6t30</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>0AM325473</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>3990</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
         </is>
       </c>
+      <c r="Q7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>0am325091e-set</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>8850</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
         </is>
       </c>
+      <c r="Q8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>0am325091f-set</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>0am325091f</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>8850</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
         </is>
       </c>
+      <c r="Q9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>7500</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
         </is>
       </c>
+      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>8500</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
+      <c r="Q11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>9500</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
+      <c r="Q12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>8500</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="2" t="n">
         <v>13000</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
+      <c r="Q13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>8500</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
         </is>
       </c>
+      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>2850</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
         </is>
       </c>
+      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>pylniki-shtokov-orig</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>1850</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
         </is>
       </c>
+      <c r="Q16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>salniki-shtokov-orig</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>1890</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
         </is>
       </c>
+      <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>salnik-shtoka-orig</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>1490</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
         </is>
       </c>
+      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="2" t="n">
         <v>1490</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
         </is>
       </c>
+      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="2" t="n">
         <v>990</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
         </is>
       </c>
+      <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>2490</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
         </is>
       </c>
+      <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>0am325025D</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="2" t="n">
         <v>4990</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="2" t="n">
         <v>7000</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
         </is>
       </c>
+      <c r="Q22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="2" t="n">
         <v>1690</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="2" t="n">
         <v>2800</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
         </is>
       </c>
+      <c r="Q23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0am325025P</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
         </is>
       </c>
+      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>0am325477ae</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="2" t="n">
         <v>2890</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
         </is>
       </c>
+      <c r="Q25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>0AM325587E</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="2" t="n">
         <v>8890</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
         </is>
       </c>
+      <c r="Q26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
         </is>
       </c>
+      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="2" t="n">
         <v>1950</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
         </is>
       </c>
+      <c r="Q28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>0am325066AC</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="2" t="n">
         <v>7400</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
         </is>
       </c>
+      <c r="Q29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>0BH325183 B</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="2" t="n">
         <v>3879</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
         </is>
       </c>
+      <c r="Q30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="2" t="n">
         <v>1950</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
         </is>
       </c>
+      <c r="Q31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>0AM325413A</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>8900</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
         </is>
       </c>
+      <c r="Q32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="2" t="n">
         <v>9500</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="2" t="n">
         <v>13500</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png</t>
         </is>
       </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="2" t="n">
         <v>3990</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Цена — грубая оценка Клода (аналогичного готового комплекта именно с усиленными поршнями в файле раньше не было, ориентировался на цену поршня по отдельности + похожий комплект с сальниками вместо поршней) — проверьте и поправьте сами.</t>
         </is>
       </c>
+      <c r="Q34" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -583,7 +583,9 @@
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="O2" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Подтверждено пользователем: это целый мехатроник в сборе с электронной платой (DQ250/DSG6), не отдельная плата. Образец поменяла на 0am325025HX — тоже 'мехатроник с эл. платой в сборе', ближе по смыслу, чем фильтр 02E305051C.</t>
@@ -634,7 +636,9 @@
         </is>
       </c>
       <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="O3" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (та же формулировка, что в seo_keywords.xlsx). Образец 0AM325413A — тоже сальник той же линейки, категория/атрибуты должны подойти.</t>
@@ -685,7 +689,9 @@
         </is>
       </c>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики. Образец 0AM325413A — тоже сальник той же линейки.</t>
@@ -736,7 +742,9 @@
         </is>
       </c>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="O5" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Название взято из уже собранной семантики (сальник входного вала).</t>
@@ -787,7 +795,9 @@
         </is>
       </c>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК — в собранной семантике есть 'сальник первичного вала' и 'сальник входного вала', но не 'выходного'. Уточни, это точно отдельная деталь (выходной/вторичный вал) или это то же самое, что 'первичный вал' у вас в терминологии?</t>
@@ -838,7 +848,9 @@
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Образец — 0AM325473 (Соленоиды мехатроника DSG7 DQ200 0AM 0CW), по твоему решению: категория/характеристики 'соленоидов' в Ozon, скорее всего, достаточно общие, чтобы не заводить отдельно через кабинет. Категорию/атрибуты после создания стоит один раз проверить в кабинете Ozon — если что-то не подойдёт (например размеры/вес явно другие для 6T30), поправим вручную.</t>
@@ -889,7 +901,9 @@
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 длинных штока 101мм 0AM325091E усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091e. Проверить вес/габариты упаковки под комплект (больше, чем у одиночного штока).</t>
@@ -940,7 +954,9 @@
         </is>
       </c>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Из архива дизайнера (Маркетплейсы.zip, папка 1). Комплект на замену: 2 коротких штока 99мм 0AM325091F усиленные с доп. резинкой + 2 новые втулки (гильзы) без задиров и царапин. Образец для по-образцу — уже существующий одиночный шток 0am325091f. Проверить вес/габариты упаковки под комплект.</t>
@@ -991,7 +1007,9 @@
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
+      <c r="O10" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита (усиленная, аналог) + фильтр в комплекте. Образец — плита 0am325066ae, пересчитать вес/габариты на 2 предмета.</t>
@@ -1042,7 +1060,9 @@
         </is>
       </c>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника (неоригинал). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -1093,7 +1113,9 @@
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+      <c r="O12" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Плита + фильтр + 2 пыльника + 2 сальника (неоригинал, полный ремкомплект). Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -1144,7 +1166,9 @@
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
+      <c r="O13" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Плита (усиленная) + фильтр + 2 пыльника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -1195,7 +1219,9 @@
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2 (2 фото одного товара). Плита (усиленная) + фильтр + 2 сальника оригинал VW Германия. Образец — 0am325066ae, пересчитать вес/габариты.</t>
@@ -1246,7 +1272,9 @@
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
+      <c r="O15" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Оригинал VAG версия существующего аналогового ремкомплекта 0am325025G. Уточнить у поставщика реальную оригинальность/цену закупки.</t>
@@ -1297,7 +1325,9 @@
         </is>
       </c>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
+      <c r="O16" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только пыльники (без сальников и крышек), оригинал VAG.</t>
@@ -1348,7 +1378,9 @@
         </is>
       </c>
       <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
+      <c r="O17" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5. Только сальники (без пыльников и крышек), оригинал VAG.</t>
@@ -1399,7 +1431,9 @@
         </is>
       </c>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
+      <c r="O18" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 3 и 5 (2 фото). Оригинал VAG версия обычного аналогового сальника 0AM325413A.</t>
@@ -1450,7 +1484,9 @@
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+      <c r="O19" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Оригинал VAG версия существующего аналога 123014-AF.</t>
@@ -1501,7 +1537,9 @@
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+      <c r="O20" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только пластины на соленоиды, оригинал VW, без сепараторной пластины (в отличие от связки 0am325025j).</t>
@@ -1552,7 +1590,9 @@
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="O21" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папки 1 и 3 (2 фото). Премиум-вариант обычного сальника толкателя 0AM325413A — алюминиевый корпус с гальваническим покрытием.</t>
@@ -1603,7 +1643,9 @@
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
+      <c r="O22" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Только втулки (без штоков), комплект 2 шт — в отличие от одиночной втулки 0am325025D.</t>
@@ -1654,7 +1696,9 @@
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
+      <c r="O23" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Только сальники штоков (без пыльников/крышек), комплект 2 шт, аналог (не оригинал).</t>
@@ -1705,7 +1749,9 @@
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Комплект из 2 клипс — в отличие от одиночной клипсы 0am325025P.</t>
@@ -1756,7 +1802,9 @@
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+      <c r="O25" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 2. Комплект 2 шт — в отличие от одиночной планки 0am325477ae (1 шт).</t>
@@ -1807,7 +1855,9 @@
         </is>
       </c>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
+      <c r="O26" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 5 (3 фото, использовал 2). Оригинал VAG версия существующего гидроаккумулятора 0AM325587E.</t>
@@ -1858,7 +1908,9 @@
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
+      <c r="O27" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4 (2 фото — 'подшипник' и 'подшипники', похоже один и тот же товар). Совсем новая категория, аналогов в каталоге нет. Образец взял 0ambset (тоже подшипники) — категория/атрибуты нужно перепроверить вручную в кабинете Ozon.</t>
@@ -1909,7 +1961,9 @@
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="O28" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 4. Новая деталь, аналогов в каталоге нет. Образец — плита 0am325066ae, проверить категорию/атрибуты вручную.</t>
@@ -1960,7 +2014,9 @@
         </is>
       </c>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="O29" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t>Архив дизайнера, папка 3. Полный комплект на все 4 позиции мехатроника — в отличие от одиночного толкателя 0am325066AC. Пересчитать вес/габариты.</t>
@@ -2011,7 +2067,9 @@
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Найден через next.png/next-2.png ещё раньше. Отдельный корпус фильтра 0BH325159 — сейчас в каталоге есть только 0BH325183B (сам фильтр) и наборы DQ500/DQ500-a/Dq500 (корпус+фильтр вместе). Образец — 0BH325183B.</t>
@@ -2062,7 +2120,9 @@
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+      <c r="O31" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
@@ -2113,7 +2173,9 @@
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="O32" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Фото — из архива дизайнера, ранее ошибочно было прикреплено к 0AM325413A вместе с фото других комплектов; вынесено в отдельную позицию.</t>
@@ -2164,7 +2226,9 @@
         </is>
       </c>
       <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
+      <c r="O33" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
     </row>
@@ -2211,7 +2275,9 @@
         </is>
       </c>
       <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="O34" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Цена — грубая оценка Клода (аналогичного готового комплекта именно с усиленными поршнями в файле раньше не было, ориентировался на цену поршня по отдельности + похожий комплект с сальниками вместо поршней) — проверьте и поправьте сами.</t>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1739,10 +1739,18 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
+      <c r="I24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png</t>

--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -967,7 +967,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
